--- a/כמותי.xlsx
+++ b/כמותי.xlsx
@@ -5,20 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dvir\תחקור פסיכומטרי\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dvir\psychometricInvestigationWithGit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE5A1BED-0499-4B91-8152-B38F414D3F5D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD5DE61-4F71-4C98-AD49-961FA2585B18}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="דוגמית לטאב" sheetId="5" r:id="rId1"/>
-    <sheet name="תכונות מספרים" sheetId="12" r:id="rId2"/>
+    <sheet name="דוגמית לטאב" sheetId="14" r:id="rId1"/>
+    <sheet name="תכונות מספרים" sheetId="15" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'דוגמית לטאב'!$B$2:$F$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'תכונות מספרים'!$B$2:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'דוגמית לטאב'!$B$2:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'תכונות מספרים'!$B$2:$G$2</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
   <si>
     <t>למה טעיתי</t>
   </si>
@@ -41,25 +41,13 @@
     <t>איך אשתפר</t>
   </si>
   <si>
-    <t>ספר הטעות</t>
-  </si>
-  <si>
     <t>עמוד ושאלת הטעות</t>
   </si>
   <si>
-    <t>אלגברה וגיאומטריה</t>
-  </si>
-  <si>
-    <t>ידע</t>
-  </si>
-  <si>
-    <t>עמוד 122 שאלה 4</t>
-  </si>
-  <si>
-    <t>אזכור ש3 מספרים עוקבים מתחלקים ב6 ו4 ב24</t>
-  </si>
-  <si>
-    <t>לא זכרתי ש4 מספרים עוקבים מתחלקים ב24</t>
+    <t>הפלוס במה שעשיתי</t>
+  </si>
+  <si>
+    <t>מיקום כללי של הטעות</t>
   </si>
 </sst>
 </file>
@@ -391,42 +379,47 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4AEE827-035F-48C6-B2F2-CF9271AF7B67}">
-  <dimension ref="B2:F2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ED8C040-4361-40D2-A54B-6ECBA7350B4B}">
+  <dimension ref="B2:G2"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="20.69921875" customWidth="1"/>
-    <col min="4" max="4" width="40.69921875" customWidth="1"/>
-    <col min="5" max="5" width="20.69921875" customWidth="1"/>
-    <col min="6" max="6" width="40.69921875" customWidth="1"/>
+    <col min="2" max="2" width="40.69921875" customWidth="1"/>
+    <col min="3" max="3" width="18.69921875" customWidth="1"/>
+    <col min="4" max="4" width="17.69921875" customWidth="1"/>
+    <col min="5" max="5" width="40.69921875" customWidth="1"/>
+    <col min="6" max="6" width="17.69921875" customWidth="1"/>
+    <col min="7" max="7" width="40.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:F2" xr:uid="{9143E0B2-37ED-40BA-BF74-A880F10CB732}"/>
+  <autoFilter ref="B2:G2" xr:uid="{87CB5822-66D4-452B-A3EB-3E11EDA85BE8}"/>
   <dataConsolidate/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{EE27D4B7-642F-434F-A73B-A32F69E4DB31}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1 F3:F1048576" xr:uid="{DBECB60C-6B8F-4EC4-BC7D-BFDD3056BA1F}">
       <formula1>"ידע, הבנה, כאפה"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{AAB13882-3EFF-4A7C-80C9-A055A70B9A48}">
-      <formula1>"חשיבה פסיכומטרית, אלגברה וגיאומטריה, שאלות ובעיות, סימולציה 1, סימולציה 2, סימולציה 3, סימולציה 4, סימולציה 5, סימולציה 6, סימולציה 7, סימולציה 8, סימולציה 9"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576" xr:uid="{7BF493EB-AF19-4587-8B44-8C950A4B16A0}">
+      <formula1>"חשיבה פסיכומטרית, ספר אלגברה וגיאומטריה, ספר שאלות ובעיות, גל 1, גל 2, גל 3, בחנים חמים מהתנור, סימולציה 1, סימולציה 2, סימולציה 3, סימולציה 4, סימולציה 5, סימולציה 6, סימולציה 7, סימולציה 8, סימולציה 9"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -435,58 +428,46 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{013BD43D-6B90-4D2B-838C-F64CA912F963}">
-  <dimension ref="B2:F4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E132A91-BD63-4135-BD52-EC7AF5CEDAC9}">
+  <dimension ref="B2:G2"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="20.69921875" customWidth="1"/>
-    <col min="4" max="4" width="40.69921875" customWidth="1"/>
-    <col min="5" max="5" width="20.69921875" customWidth="1"/>
-    <col min="6" max="6" width="40.69921875" customWidth="1"/>
+    <col min="2" max="2" width="40.69921875" customWidth="1"/>
+    <col min="3" max="3" width="18.69921875" customWidth="1"/>
+    <col min="4" max="4" width="17.69921875" customWidth="1"/>
+    <col min="5" max="5" width="40.69921875" customWidth="1"/>
+    <col min="6" max="6" width="17.69921875" customWidth="1"/>
+    <col min="7" max="7" width="40.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:F2" xr:uid="{9143E0B2-37ED-40BA-BF74-A880F10CB732}"/>
+  <autoFilter ref="B2:G2" xr:uid="{87CB5822-66D4-452B-A3EB-3E11EDA85BE8}"/>
   <dataConsolidate/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{24CE509D-0918-4110-A046-184F1C580D79}">
-      <formula1>"חשיבה פסיכומטרית, אלגברה וגיאומטריה, שאלות ובעיות, סימולציה 1, סימולציה 2, סימולציה 3, סימולציה 4, סימולציה 5, סימולציה 6, סימולציה 7, סימולציה 8, סימולציה 9"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576" xr:uid="{46599F15-22B1-4A6F-8280-973AC6F2DAC4}">
+      <formula1>"חשיבה פסיכומטרית, ספר אלגברה וגיאומטריה, ספר שאלות ובעיות, גל 1, גל 2, גל 3, בחנים חמים מהתנור, סימולציה 1, סימולציה 2, סימולציה 3, סימולציה 4, סימולציה 5, סימולציה 6, סימולציה 7, סימולציה 8, סימולציה 9"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{ED0F5CE6-4D97-4325-A06F-FCAE311EE9D2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1 F3:F1048576" xr:uid="{08FF2842-B413-4AD5-897E-72A800DCD2B8}">
       <formula1>"ידע, הבנה, כאפה"</formula1>
     </dataValidation>
   </dataValidations>

--- a/כמותי.xlsx
+++ b/כמותי.xlsx
@@ -8,16 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dvir\psychometricInvestigationWithGit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD5DE61-4F71-4C98-AD49-961FA2585B18}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D7EA56D-1C52-404F-8058-F641A3E709B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="דוגמית לטאב" sheetId="14" r:id="rId1"/>
     <sheet name="תכונות מספרים" sheetId="15" r:id="rId2"/>
+    <sheet name="אחוזים" sheetId="16" r:id="rId3"/>
+    <sheet name="גיאומטריה" sheetId="17" r:id="rId4"/>
+    <sheet name="השוואת שברים" sheetId="19" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">אחוזים!$B$2:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">גיאומטריה!$B$2:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'דוגמית לטאב'!$B$2:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'השוואת שברים'!$B$2:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'תכונות מספרים'!$B$2:$G$2</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -30,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="71">
   <si>
     <t>למה טעיתי</t>
   </si>
@@ -48,6 +54,201 @@
   </si>
   <si>
     <t>מיקום כללי של הטעות</t>
+  </si>
+  <si>
+    <t>פירקתי את הנתון לנתון פשוט יותר</t>
+  </si>
+  <si>
+    <t>ספר אלגברה וגיאומטריה</t>
+  </si>
+  <si>
+    <t>עמוד 123 שאלה 11</t>
+  </si>
+  <si>
+    <t>לא קראתי את השאלה כמו שצריך</t>
+  </si>
+  <si>
+    <t>הבנה</t>
+  </si>
+  <si>
+    <t>לקרוא את השאלה ולכתוב מה שהבנו או פשוט לקרוא בעיון</t>
+  </si>
+  <si>
+    <t>לקרוא את השאלה ולהבין אותה. אפילו לסמן מילים חשובות</t>
+  </si>
+  <si>
+    <t>זכרתי שמכפלת שלוש מספרים עוקבים מתחלקת ב6</t>
+  </si>
+  <si>
+    <t>כאפה</t>
+  </si>
+  <si>
+    <t>לקרוא את השאלה ולסמן קו מתחת למילים חשובות.</t>
+  </si>
+  <si>
+    <t>עמוד 126 שאלה 15</t>
+  </si>
+  <si>
+    <t>לא וויתרתי ואפילו ניסיתי לחשוב על דרך מחוץ לקופסא</t>
+  </si>
+  <si>
+    <t>עמוד 127 שאלה 23</t>
+  </si>
+  <si>
+    <t>ידע</t>
+  </si>
+  <si>
+    <t>לזכור שממוצע על מספר זוגי של מספרים עוקבים זה קצוות חלקי 2</t>
+  </si>
+  <si>
+    <t>שכחתי שעושים ממוצע של מספר זוגי של מספרים עוקבים</t>
+  </si>
+  <si>
+    <t>חישבתי בדרך הeasy וקראתי טוב את השאלה</t>
+  </si>
+  <si>
+    <t>עמוד 127 שאלה 24</t>
+  </si>
+  <si>
+    <t>לא חישבתי נכון חישוב מתמטי בסיסי</t>
+  </si>
+  <si>
+    <t>לכתוב חישובים שאני עושה אם הם לא כל כך פשוטים</t>
+  </si>
+  <si>
+    <t>פישטתי את הביטוי</t>
+  </si>
+  <si>
+    <t>עמוד 127 שאלה 28</t>
+  </si>
+  <si>
+    <t>לא חשבתי מספיק והייתי פזיז</t>
+  </si>
+  <si>
+    <t>לרשום דברים שאני אראה בעיניים מה צריך להיות התשובה</t>
+  </si>
+  <si>
+    <t>לא חישבתי כמו טמבל וקלטתי שיש משחק עם החזקת 25</t>
+  </si>
+  <si>
+    <t>עמוד 130 שאלה 33</t>
+  </si>
+  <si>
+    <t>לא התעמקתי מספיק בשאלה וגם הייתי צריך לזכור לחשוב על הגורמים של המכפלה בישביל לדעת במה מתחלק</t>
+  </si>
+  <si>
+    <t>לזכור שכששואלים במה יתחלק ויש ביטוי ארוך של כפל לשים לב לגורמים של אותו הכפל ובתשובות ולראות לפי זה מה מתאים.</t>
+  </si>
+  <si>
+    <t>זיהיתי שדווקא זו שאלת יחסים וסיווגתי שהשאלה היא יחס פשוט</t>
+  </si>
+  <si>
+    <t>עמוד 130 שאלה 35</t>
+  </si>
+  <si>
+    <t>כי לא חישבתי עם יחידות יחס ולא שמתי לב שמדובר על היחס בין העגילים למחברות</t>
+  </si>
+  <si>
+    <t>לזכור שביחס עושים יחידת יחס ואז אם יש עוד יחס שמראה נתון על יחידת היחס אז צריך להשתמש בזה. בנוסף, כדי לקרוא את השאלה ובייחוד את הדבר שצריך בסוף.</t>
+  </si>
+  <si>
+    <t>הבנתי שחשוב להבין כמה כורסאות הוא מכר</t>
+  </si>
+  <si>
+    <t>עמוד 130 שאלה 36</t>
+  </si>
+  <si>
+    <t>לא ניסיתי לראות אם 512 מתחלק ב3</t>
+  </si>
+  <si>
+    <t>כדאי לבדוק כמה מוצרים גדולים יכול להיות שקנו ולזכור שסכום של מספר שמתחלק ואחד שלא מתחלק ב3, לא מתחלק ב3</t>
+  </si>
+  <si>
+    <t>ניסיתי בדרך  של הצבת תשובות ולא ויתרתי</t>
+  </si>
+  <si>
+    <t>עמוד 5 שאלה 12</t>
+  </si>
+  <si>
+    <t>לא הבנתי מה השלם בשאלה וזה שהשאלה היא מסוג גדול מ קטן מ</t>
+  </si>
+  <si>
+    <t>אזכור שבכמה גדל וגם קטן זה מהמספר הקדום ובכללי להבין שזה חלק משאלות גדול מ קטן מ</t>
+  </si>
+  <si>
+    <t>כתבתי ברור ועשיתי בדרך הנכונה</t>
+  </si>
+  <si>
+    <t>עמוד 9 שאלה 18</t>
+  </si>
+  <si>
+    <t>פשוט עשיתי טעות בחישוב</t>
+  </si>
+  <si>
+    <t>לשים לב לתרגיל שעשיתי ולא להיות פזיז</t>
+  </si>
+  <si>
+    <t>הקפתי תשובה ובמקרה היא גם נכונה</t>
+  </si>
+  <si>
+    <t>עמוד 13 שאלה 34</t>
+  </si>
+  <si>
+    <t>לא קראתי את השאלה טוב</t>
+  </si>
+  <si>
+    <t>לקרוא טוב את השאלה ולסמן את המילים אם יש הרבה מלל</t>
+  </si>
+  <si>
+    <t>ספר שאלות ובעיות</t>
+  </si>
+  <si>
+    <t>כתבתי את הנתונים על הסרטוט</t>
+  </si>
+  <si>
+    <t>עמוד 202 שאלה 17</t>
+  </si>
+  <si>
+    <t>כי לא סימנתי את הנתונים כמו שצריך ולא ידעתי שקטע אמצעים חוצה את הגובה גם ואם הוא מקביל וחוצה את הגובה אז הוא קטע אמצעים</t>
+  </si>
+  <si>
+    <t>אלמד את המשפט שאמרתי וגם אסמן את הנתונים</t>
+  </si>
+  <si>
+    <t>זכרתי את תכונות משולש הזהב והגעתי לתשובה נכונה</t>
+  </si>
+  <si>
+    <t>עמוד 205 שאלה 28</t>
+  </si>
+  <si>
+    <t>לא ידעתי ששורש לעולם לא יופיע במכנה בתשובות בפסיכומטרי</t>
+  </si>
+  <si>
+    <t>אזכור את הכלל של השורש במכנה ומתוך כך אחפש להרחיב את התשובה שקיבלתי כך שהיא תתאים לתשובה הנכונה במבחן.</t>
+  </si>
+  <si>
+    <t>פשוט ניחשתי תוצאה וניסיתי לעשות את שיטות הeasy</t>
+  </si>
+  <si>
+    <t>עמוד 96</t>
+  </si>
+  <si>
+    <t>לא ידעתי שכשהשיטות לא עובדות פשוט מנסים להשוות לשבר קלאסי כמו חצי ולראות אם אחד יותר גדול ואחד פחות</t>
+  </si>
+  <si>
+    <t>אזכור שכשאין שיטה משווים את שני השברים לשבר קלאסי</t>
+  </si>
+  <si>
+    <t>כתבתי ליד כל שבר את הצמצום שלו והשתמשתי בשיטות</t>
+  </si>
+  <si>
+    <t>עמוד 97 שאלה 12</t>
+  </si>
+  <si>
+    <t>טעות בחישוב</t>
+  </si>
+  <si>
+    <t>אשים לב לחישובים שאני עושה ואמנע מחישוב בראש.</t>
   </si>
 </sst>
 </file>
@@ -97,9 +298,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -380,7 +585,539 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ED8C040-4361-40D2-A54B-6ECBA7350B4B}">
-  <dimension ref="B2:G2"/>
+  <dimension ref="B1:G3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="40.69921875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18.69921875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.69921875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="40.69921875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.69921875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="40.69921875" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B1"/>
+      <c r="C1"/>
+      <c r="D1"/>
+      <c r="E1"/>
+      <c r="F1"/>
+      <c r="G1"/>
+    </row>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="B2:G2" xr:uid="{87CB5822-66D4-452B-A3EB-3E11EDA85BE8}"/>
+  <dataConsolidate/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F1048576" xr:uid="{DBECB60C-6B8F-4EC4-BC7D-BFDD3056BA1F}">
+      <formula1>"ידע, הבנה, כאפה"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C1048576" xr:uid="{7BF493EB-AF19-4587-8B44-8C950A4B16A0}">
+      <formula1>"ספר חשיבה פסיכומטרית, ספר אלגברה וגיאומטריה, ספר שאלות ובעיות, גל 1, גל 2, גל 3, בחנים חמים מהתנור, סימולציה 1, סימולציה 2, סימולציה 3, סימולציה 4, סימולציה 5, סימולציה 6, סימולציה 7, סימולציה 8, סימולציה 9"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E132A91-BD63-4135-BD52-EC7AF5CEDAC9}">
+  <dimension ref="A2:G95"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.796875" style="3"/>
+    <col min="2" max="2" width="40.69921875" customWidth="1"/>
+    <col min="3" max="3" width="18.69921875" customWidth="1"/>
+    <col min="4" max="4" width="17.69921875" customWidth="1"/>
+    <col min="5" max="5" width="40.69921875" customWidth="1"/>
+    <col min="6" max="6" width="17.69921875" customWidth="1"/>
+    <col min="7" max="7" width="40.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="B7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="2" customFormat="1" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="B8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="2" customFormat="1" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="B9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="2" customFormat="1" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="B10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="2" customFormat="1" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+    </row>
+    <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3"/>
+    </row>
+    <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3"/>
+    </row>
+    <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
+    </row>
+    <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3"/>
+    </row>
+    <row r="17" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+    </row>
+    <row r="18" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3"/>
+    </row>
+    <row r="19" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3"/>
+    </row>
+    <row r="20" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3"/>
+    </row>
+    <row r="21" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3"/>
+    </row>
+    <row r="22" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3"/>
+    </row>
+    <row r="23" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3"/>
+    </row>
+    <row r="24" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3"/>
+    </row>
+    <row r="25" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3"/>
+    </row>
+    <row r="26" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
+    </row>
+    <row r="27" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3"/>
+    </row>
+    <row r="28" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3"/>
+    </row>
+    <row r="29" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3"/>
+    </row>
+    <row r="30" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3"/>
+    </row>
+    <row r="31" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3"/>
+    </row>
+    <row r="32" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3"/>
+    </row>
+    <row r="33" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3"/>
+    </row>
+    <row r="34" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3"/>
+    </row>
+    <row r="35" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3"/>
+    </row>
+    <row r="36" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3"/>
+    </row>
+    <row r="38" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3"/>
+    </row>
+    <row r="39" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3"/>
+    </row>
+    <row r="40" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="3"/>
+    </row>
+    <row r="41" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="3"/>
+    </row>
+    <row r="45" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="3"/>
+    </row>
+    <row r="46" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="3"/>
+    </row>
+    <row r="47" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="3"/>
+    </row>
+    <row r="48" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3"/>
+    </row>
+    <row r="51" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="3"/>
+    </row>
+    <row r="52" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="3"/>
+    </row>
+    <row r="53" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="3"/>
+    </row>
+    <row r="54" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="3"/>
+    </row>
+    <row r="55" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="3"/>
+    </row>
+    <row r="56" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="3"/>
+    </row>
+    <row r="57" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="3"/>
+    </row>
+    <row r="58" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="3"/>
+    </row>
+    <row r="59" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="3"/>
+    </row>
+    <row r="60" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="3"/>
+    </row>
+    <row r="61" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="3"/>
+    </row>
+    <row r="62" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="3"/>
+    </row>
+    <row r="63" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="3"/>
+    </row>
+    <row r="64" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="3"/>
+    </row>
+    <row r="65" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="3"/>
+    </row>
+    <row r="66" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="3"/>
+    </row>
+    <row r="67" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="3"/>
+    </row>
+    <row r="68" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="3"/>
+    </row>
+    <row r="69" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="3"/>
+    </row>
+    <row r="70" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="3"/>
+    </row>
+    <row r="71" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="3"/>
+    </row>
+    <row r="72" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="3"/>
+    </row>
+    <row r="73" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="3"/>
+    </row>
+    <row r="74" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="3"/>
+    </row>
+    <row r="75" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="3"/>
+    </row>
+    <row r="76" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="3"/>
+    </row>
+    <row r="77" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="3"/>
+    </row>
+    <row r="78" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="3"/>
+    </row>
+    <row r="79" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="3"/>
+    </row>
+    <row r="80" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="3"/>
+    </row>
+    <row r="81" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="3"/>
+    </row>
+    <row r="82" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="3"/>
+    </row>
+    <row r="83" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="3"/>
+    </row>
+    <row r="84" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="3"/>
+    </row>
+    <row r="85" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="3"/>
+    </row>
+    <row r="86" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="3"/>
+    </row>
+    <row r="87" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="3"/>
+    </row>
+    <row r="88" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="3"/>
+    </row>
+    <row r="89" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="3"/>
+    </row>
+    <row r="90" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="3"/>
+    </row>
+    <row r="91" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="3"/>
+    </row>
+    <row r="92" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="3"/>
+    </row>
+    <row r="93" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="3"/>
+    </row>
+    <row r="94" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="3"/>
+    </row>
+    <row r="95" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="3"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="B2:G2" xr:uid="{87CB5822-66D4-452B-A3EB-3E11EDA85BE8}"/>
+  <dataConsolidate/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F11 F13:F1048576" xr:uid="{08FF2842-B413-4AD5-897E-72A800DCD2B8}">
+      <formula1>"ידע, הבנה, כאפה"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C13:C1048576 C4:C11" xr:uid="{46599F15-22B1-4A6F-8280-973AC6F2DAC4}">
+      <formula1>"חשיבה פסיכומטרית, ספר אלגברה וגיאומטריה, ספר שאלות ובעיות, גל 1, גל 2, גל 3, בחנים חמים מהתנור, סימולציה 1, סימולציה 2, סימולציה 3, סימולציה 4, סימולציה 5, סימולציה 6, סימולציה 7, סימולציה 8, סימולציה 9"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{784778E9-CD7C-47AA-A7BA-9ED8101585C3}">
+  <dimension ref="B2:G208"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="40.69921875" customWidth="1"/>
@@ -411,15 +1148,1699 @@
         <v>2</v>
       </c>
     </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="2:7" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+    </row>
+    <row r="70" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+    </row>
+    <row r="71" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+    </row>
+    <row r="72" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+    </row>
+    <row r="73" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+    </row>
+    <row r="74" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+    </row>
+    <row r="75" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+    </row>
+    <row r="76" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+    </row>
+    <row r="77" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+    </row>
+    <row r="78" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+    </row>
+    <row r="79" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+    </row>
+    <row r="80" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+    </row>
+    <row r="81" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+    </row>
+    <row r="82" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+    </row>
+    <row r="83" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+    </row>
+    <row r="84" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+    </row>
+    <row r="85" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+    </row>
+    <row r="86" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+    </row>
+    <row r="87" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+    </row>
+    <row r="88" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+    </row>
+    <row r="89" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+    </row>
+    <row r="90" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+    </row>
+    <row r="91" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+    </row>
+    <row r="92" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+    </row>
+    <row r="93" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+    </row>
+    <row r="94" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+    </row>
+    <row r="95" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+    </row>
+    <row r="96" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+    </row>
+    <row r="97" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+    </row>
+    <row r="98" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+    </row>
+    <row r="99" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+    </row>
+    <row r="100" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+    </row>
+    <row r="101" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+    </row>
+    <row r="102" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+    </row>
+    <row r="103" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+    </row>
+    <row r="104" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+    </row>
+    <row r="105" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+    </row>
+    <row r="106" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+    </row>
+    <row r="107" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+    </row>
+    <row r="108" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B108" s="2"/>
+      <c r="C108" s="2"/>
+      <c r="D108" s="2"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2"/>
+      <c r="G108" s="2"/>
+    </row>
+    <row r="109" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="2"/>
+      <c r="F109" s="2"/>
+      <c r="G109" s="2"/>
+    </row>
+    <row r="110" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B110" s="2"/>
+      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="2"/>
+      <c r="F110" s="2"/>
+      <c r="G110" s="2"/>
+    </row>
+    <row r="111" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B111" s="2"/>
+      <c r="C111" s="2"/>
+      <c r="D111" s="2"/>
+      <c r="E111" s="2"/>
+      <c r="F111" s="2"/>
+      <c r="G111" s="2"/>
+    </row>
+    <row r="112" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
+      <c r="D112" s="2"/>
+      <c r="E112" s="2"/>
+      <c r="F112" s="2"/>
+      <c r="G112" s="2"/>
+    </row>
+    <row r="113" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B113" s="2"/>
+      <c r="C113" s="2"/>
+      <c r="D113" s="2"/>
+      <c r="E113" s="2"/>
+      <c r="F113" s="2"/>
+      <c r="G113" s="2"/>
+    </row>
+    <row r="114" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
+      <c r="D114" s="2"/>
+      <c r="E114" s="2"/>
+      <c r="F114" s="2"/>
+      <c r="G114" s="2"/>
+    </row>
+    <row r="115" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B115" s="2"/>
+      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="2"/>
+      <c r="G115" s="2"/>
+    </row>
+    <row r="116" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B116" s="2"/>
+      <c r="C116" s="2"/>
+      <c r="D116" s="2"/>
+      <c r="E116" s="2"/>
+      <c r="F116" s="2"/>
+      <c r="G116" s="2"/>
+    </row>
+    <row r="117" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B117" s="2"/>
+      <c r="C117" s="2"/>
+      <c r="D117" s="2"/>
+      <c r="E117" s="2"/>
+      <c r="F117" s="2"/>
+      <c r="G117" s="2"/>
+    </row>
+    <row r="118" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B118" s="2"/>
+      <c r="C118" s="2"/>
+      <c r="D118" s="2"/>
+      <c r="E118" s="2"/>
+      <c r="F118" s="2"/>
+      <c r="G118" s="2"/>
+    </row>
+    <row r="119" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B119" s="2"/>
+      <c r="C119" s="2"/>
+      <c r="D119" s="2"/>
+      <c r="E119" s="2"/>
+      <c r="F119" s="2"/>
+      <c r="G119" s="2"/>
+    </row>
+    <row r="120" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B120" s="2"/>
+      <c r="C120" s="2"/>
+      <c r="D120" s="2"/>
+      <c r="E120" s="2"/>
+      <c r="F120" s="2"/>
+      <c r="G120" s="2"/>
+    </row>
+    <row r="121" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B121" s="2"/>
+      <c r="C121" s="2"/>
+      <c r="D121" s="2"/>
+      <c r="E121" s="2"/>
+      <c r="F121" s="2"/>
+      <c r="G121" s="2"/>
+    </row>
+    <row r="122" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B122" s="2"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
+      <c r="E122" s="2"/>
+      <c r="F122" s="2"/>
+      <c r="G122" s="2"/>
+    </row>
+    <row r="123" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B123" s="2"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="2"/>
+      <c r="E123" s="2"/>
+      <c r="F123" s="2"/>
+      <c r="G123" s="2"/>
+    </row>
+    <row r="124" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B124" s="2"/>
+      <c r="C124" s="2"/>
+      <c r="D124" s="2"/>
+      <c r="E124" s="2"/>
+      <c r="F124" s="2"/>
+      <c r="G124" s="2"/>
+    </row>
+    <row r="125" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B125" s="2"/>
+      <c r="C125" s="2"/>
+      <c r="D125" s="2"/>
+      <c r="E125" s="2"/>
+      <c r="F125" s="2"/>
+      <c r="G125" s="2"/>
+    </row>
+    <row r="126" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B126" s="2"/>
+      <c r="C126" s="2"/>
+      <c r="D126" s="2"/>
+      <c r="E126" s="2"/>
+      <c r="F126" s="2"/>
+      <c r="G126" s="2"/>
+    </row>
+    <row r="127" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B127" s="2"/>
+      <c r="C127" s="2"/>
+      <c r="D127" s="2"/>
+      <c r="E127" s="2"/>
+      <c r="F127" s="2"/>
+      <c r="G127" s="2"/>
+    </row>
+    <row r="128" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B128" s="2"/>
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
+      <c r="E128" s="2"/>
+      <c r="F128" s="2"/>
+      <c r="G128" s="2"/>
+    </row>
+    <row r="129" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B129" s="2"/>
+      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="2"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="2"/>
+    </row>
+    <row r="130" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B130" s="2"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="2"/>
+      <c r="F130" s="2"/>
+      <c r="G130" s="2"/>
+    </row>
+    <row r="131" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B131" s="2"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="2"/>
+      <c r="E131" s="2"/>
+      <c r="F131" s="2"/>
+      <c r="G131" s="2"/>
+    </row>
+    <row r="132" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B132" s="2"/>
+      <c r="C132" s="2"/>
+      <c r="D132" s="2"/>
+      <c r="E132" s="2"/>
+      <c r="F132" s="2"/>
+      <c r="G132" s="2"/>
+    </row>
+    <row r="133" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B133" s="2"/>
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
+      <c r="E133" s="2"/>
+      <c r="F133" s="2"/>
+      <c r="G133" s="2"/>
+    </row>
+    <row r="134" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B134" s="2"/>
+      <c r="C134" s="2"/>
+      <c r="D134" s="2"/>
+      <c r="E134" s="2"/>
+      <c r="F134" s="2"/>
+      <c r="G134" s="2"/>
+    </row>
+    <row r="135" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B135" s="2"/>
+      <c r="C135" s="2"/>
+      <c r="D135" s="2"/>
+      <c r="E135" s="2"/>
+      <c r="F135" s="2"/>
+      <c r="G135" s="2"/>
+    </row>
+    <row r="136" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B136" s="2"/>
+      <c r="C136" s="2"/>
+      <c r="D136" s="2"/>
+      <c r="E136" s="2"/>
+      <c r="F136" s="2"/>
+      <c r="G136" s="2"/>
+    </row>
+    <row r="137" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B137" s="2"/>
+      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
+      <c r="E137" s="2"/>
+      <c r="F137" s="2"/>
+      <c r="G137" s="2"/>
+    </row>
+    <row r="138" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B138" s="2"/>
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
+      <c r="E138" s="2"/>
+      <c r="F138" s="2"/>
+      <c r="G138" s="2"/>
+    </row>
+    <row r="139" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B139" s="2"/>
+      <c r="C139" s="2"/>
+      <c r="D139" s="2"/>
+      <c r="E139" s="2"/>
+      <c r="F139" s="2"/>
+      <c r="G139" s="2"/>
+    </row>
+    <row r="140" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B140" s="2"/>
+      <c r="C140" s="2"/>
+      <c r="D140" s="2"/>
+      <c r="E140" s="2"/>
+      <c r="F140" s="2"/>
+      <c r="G140" s="2"/>
+    </row>
+    <row r="141" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B141" s="2"/>
+      <c r="C141" s="2"/>
+      <c r="D141" s="2"/>
+      <c r="E141" s="2"/>
+      <c r="F141" s="2"/>
+      <c r="G141" s="2"/>
+    </row>
+    <row r="142" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B142" s="2"/>
+      <c r="C142" s="2"/>
+      <c r="D142" s="2"/>
+      <c r="E142" s="2"/>
+      <c r="F142" s="2"/>
+      <c r="G142" s="2"/>
+    </row>
+    <row r="143" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B143" s="2"/>
+      <c r="C143" s="2"/>
+      <c r="D143" s="2"/>
+      <c r="E143" s="2"/>
+      <c r="F143" s="2"/>
+      <c r="G143" s="2"/>
+    </row>
+    <row r="144" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B144" s="2"/>
+      <c r="C144" s="2"/>
+      <c r="D144" s="2"/>
+      <c r="E144" s="2"/>
+      <c r="F144" s="2"/>
+      <c r="G144" s="2"/>
+    </row>
+    <row r="145" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B145" s="2"/>
+      <c r="C145" s="2"/>
+      <c r="D145" s="2"/>
+      <c r="E145" s="2"/>
+      <c r="F145" s="2"/>
+      <c r="G145" s="2"/>
+    </row>
+    <row r="146" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B146" s="2"/>
+      <c r="C146" s="2"/>
+      <c r="D146" s="2"/>
+      <c r="E146" s="2"/>
+      <c r="F146" s="2"/>
+      <c r="G146" s="2"/>
+    </row>
+    <row r="147" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B147" s="2"/>
+      <c r="C147" s="2"/>
+      <c r="D147" s="2"/>
+      <c r="E147" s="2"/>
+      <c r="F147" s="2"/>
+      <c r="G147" s="2"/>
+    </row>
+    <row r="148" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B148" s="2"/>
+      <c r="C148" s="2"/>
+      <c r="D148" s="2"/>
+      <c r="E148" s="2"/>
+      <c r="F148" s="2"/>
+      <c r="G148" s="2"/>
+    </row>
+    <row r="149" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B149" s="2"/>
+      <c r="C149" s="2"/>
+      <c r="D149" s="2"/>
+      <c r="E149" s="2"/>
+      <c r="F149" s="2"/>
+      <c r="G149" s="2"/>
+    </row>
+    <row r="150" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
+      <c r="E150" s="2"/>
+      <c r="F150" s="2"/>
+      <c r="G150" s="2"/>
+    </row>
+    <row r="151" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B151" s="2"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
+      <c r="E151" s="2"/>
+      <c r="F151" s="2"/>
+      <c r="G151" s="2"/>
+    </row>
+    <row r="152" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B152" s="2"/>
+      <c r="C152" s="2"/>
+      <c r="D152" s="2"/>
+      <c r="E152" s="2"/>
+      <c r="F152" s="2"/>
+      <c r="G152" s="2"/>
+    </row>
+    <row r="153" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B153" s="2"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
+      <c r="E153" s="2"/>
+      <c r="F153" s="2"/>
+      <c r="G153" s="2"/>
+    </row>
+    <row r="154" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B154" s="2"/>
+      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
+      <c r="E154" s="2"/>
+      <c r="F154" s="2"/>
+      <c r="G154" s="2"/>
+    </row>
+    <row r="155" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B155" s="2"/>
+      <c r="C155" s="2"/>
+      <c r="D155" s="2"/>
+      <c r="E155" s="2"/>
+      <c r="F155" s="2"/>
+      <c r="G155" s="2"/>
+    </row>
+    <row r="156" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B156" s="2"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
+      <c r="E156" s="2"/>
+      <c r="F156" s="2"/>
+      <c r="G156" s="2"/>
+    </row>
+    <row r="157" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B157" s="2"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
+      <c r="E157" s="2"/>
+      <c r="F157" s="2"/>
+      <c r="G157" s="2"/>
+    </row>
+    <row r="158" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B158" s="2"/>
+      <c r="C158" s="2"/>
+      <c r="D158" s="2"/>
+      <c r="E158" s="2"/>
+      <c r="F158" s="2"/>
+      <c r="G158" s="2"/>
+    </row>
+    <row r="159" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B159" s="2"/>
+      <c r="C159" s="2"/>
+      <c r="D159" s="2"/>
+      <c r="E159" s="2"/>
+      <c r="F159" s="2"/>
+      <c r="G159" s="2"/>
+    </row>
+    <row r="160" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B160" s="2"/>
+      <c r="C160" s="2"/>
+      <c r="D160" s="2"/>
+      <c r="E160" s="2"/>
+      <c r="F160" s="2"/>
+      <c r="G160" s="2"/>
+    </row>
+    <row r="161" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B161" s="2"/>
+      <c r="C161" s="2"/>
+      <c r="D161" s="2"/>
+      <c r="E161" s="2"/>
+      <c r="F161" s="2"/>
+      <c r="G161" s="2"/>
+    </row>
+    <row r="162" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B162" s="2"/>
+      <c r="C162" s="2"/>
+      <c r="D162" s="2"/>
+      <c r="E162" s="2"/>
+      <c r="F162" s="2"/>
+      <c r="G162" s="2"/>
+    </row>
+    <row r="163" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B163" s="2"/>
+      <c r="C163" s="2"/>
+      <c r="D163" s="2"/>
+      <c r="E163" s="2"/>
+      <c r="F163" s="2"/>
+      <c r="G163" s="2"/>
+    </row>
+    <row r="164" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B164" s="2"/>
+      <c r="C164" s="2"/>
+      <c r="D164" s="2"/>
+      <c r="E164" s="2"/>
+      <c r="F164" s="2"/>
+      <c r="G164" s="2"/>
+    </row>
+    <row r="165" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B165" s="2"/>
+      <c r="C165" s="2"/>
+      <c r="D165" s="2"/>
+      <c r="E165" s="2"/>
+      <c r="F165" s="2"/>
+      <c r="G165" s="2"/>
+    </row>
+    <row r="166" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B166" s="2"/>
+      <c r="C166" s="2"/>
+      <c r="D166" s="2"/>
+      <c r="E166" s="2"/>
+      <c r="F166" s="2"/>
+      <c r="G166" s="2"/>
+    </row>
+    <row r="167" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B167" s="2"/>
+      <c r="C167" s="2"/>
+      <c r="D167" s="2"/>
+      <c r="E167" s="2"/>
+      <c r="F167" s="2"/>
+      <c r="G167" s="2"/>
+    </row>
+    <row r="168" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B168" s="2"/>
+      <c r="C168" s="2"/>
+      <c r="D168" s="2"/>
+      <c r="E168" s="2"/>
+      <c r="F168" s="2"/>
+      <c r="G168" s="2"/>
+    </row>
+    <row r="169" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B169" s="2"/>
+      <c r="C169" s="2"/>
+      <c r="D169" s="2"/>
+      <c r="E169" s="2"/>
+      <c r="F169" s="2"/>
+      <c r="G169" s="2"/>
+    </row>
+    <row r="170" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B170" s="2"/>
+      <c r="C170" s="2"/>
+      <c r="D170" s="2"/>
+      <c r="E170" s="2"/>
+      <c r="F170" s="2"/>
+      <c r="G170" s="2"/>
+    </row>
+    <row r="171" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B171" s="2"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="2"/>
+      <c r="E171" s="2"/>
+      <c r="F171" s="2"/>
+      <c r="G171" s="2"/>
+    </row>
+    <row r="172" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B172" s="2"/>
+      <c r="C172" s="2"/>
+      <c r="D172" s="2"/>
+      <c r="E172" s="2"/>
+      <c r="F172" s="2"/>
+      <c r="G172" s="2"/>
+    </row>
+    <row r="173" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B173" s="2"/>
+      <c r="C173" s="2"/>
+      <c r="D173" s="2"/>
+      <c r="E173" s="2"/>
+      <c r="F173" s="2"/>
+      <c r="G173" s="2"/>
+    </row>
+    <row r="174" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B174" s="2"/>
+      <c r="C174" s="2"/>
+      <c r="D174" s="2"/>
+      <c r="E174" s="2"/>
+      <c r="F174" s="2"/>
+      <c r="G174" s="2"/>
+    </row>
+    <row r="175" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B175" s="2"/>
+      <c r="C175" s="2"/>
+      <c r="D175" s="2"/>
+      <c r="E175" s="2"/>
+      <c r="F175" s="2"/>
+      <c r="G175" s="2"/>
+    </row>
+    <row r="176" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B176" s="2"/>
+      <c r="C176" s="2"/>
+      <c r="D176" s="2"/>
+      <c r="E176" s="2"/>
+      <c r="F176" s="2"/>
+      <c r="G176" s="2"/>
+    </row>
+    <row r="177" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B177" s="2"/>
+      <c r="C177" s="2"/>
+      <c r="D177" s="2"/>
+      <c r="E177" s="2"/>
+      <c r="F177" s="2"/>
+      <c r="G177" s="2"/>
+    </row>
+    <row r="178" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B178" s="2"/>
+      <c r="C178" s="2"/>
+      <c r="D178" s="2"/>
+      <c r="E178" s="2"/>
+      <c r="F178" s="2"/>
+      <c r="G178" s="2"/>
+    </row>
+    <row r="179" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B179" s="2"/>
+      <c r="C179" s="2"/>
+      <c r="D179" s="2"/>
+      <c r="E179" s="2"/>
+      <c r="F179" s="2"/>
+      <c r="G179" s="2"/>
+    </row>
+    <row r="180" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B180" s="2"/>
+      <c r="C180" s="2"/>
+      <c r="D180" s="2"/>
+      <c r="E180" s="2"/>
+      <c r="F180" s="2"/>
+      <c r="G180" s="2"/>
+    </row>
+    <row r="181" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B181" s="2"/>
+      <c r="C181" s="2"/>
+      <c r="D181" s="2"/>
+      <c r="E181" s="2"/>
+      <c r="F181" s="2"/>
+      <c r="G181" s="2"/>
+    </row>
+    <row r="182" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B182" s="2"/>
+      <c r="C182" s="2"/>
+      <c r="D182" s="2"/>
+      <c r="E182" s="2"/>
+      <c r="F182" s="2"/>
+      <c r="G182" s="2"/>
+    </row>
+    <row r="183" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B183" s="2"/>
+      <c r="C183" s="2"/>
+      <c r="D183" s="2"/>
+      <c r="E183" s="2"/>
+      <c r="F183" s="2"/>
+      <c r="G183" s="2"/>
+    </row>
+    <row r="184" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B184" s="2"/>
+      <c r="C184" s="2"/>
+      <c r="D184" s="2"/>
+      <c r="E184" s="2"/>
+      <c r="F184" s="2"/>
+      <c r="G184" s="2"/>
+    </row>
+    <row r="185" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B185" s="2"/>
+      <c r="C185" s="2"/>
+      <c r="D185" s="2"/>
+      <c r="E185" s="2"/>
+      <c r="F185" s="2"/>
+      <c r="G185" s="2"/>
+    </row>
+    <row r="186" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B186" s="2"/>
+      <c r="C186" s="2"/>
+      <c r="D186" s="2"/>
+      <c r="E186" s="2"/>
+      <c r="F186" s="2"/>
+      <c r="G186" s="2"/>
+    </row>
+    <row r="187" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B187" s="2"/>
+      <c r="C187" s="2"/>
+      <c r="D187" s="2"/>
+      <c r="E187" s="2"/>
+      <c r="F187" s="2"/>
+      <c r="G187" s="2"/>
+    </row>
+    <row r="188" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B188" s="2"/>
+      <c r="C188" s="2"/>
+      <c r="D188" s="2"/>
+      <c r="E188" s="2"/>
+      <c r="F188" s="2"/>
+      <c r="G188" s="2"/>
+    </row>
+    <row r="189" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B189" s="2"/>
+      <c r="C189" s="2"/>
+      <c r="D189" s="2"/>
+      <c r="E189" s="2"/>
+      <c r="F189" s="2"/>
+      <c r="G189" s="2"/>
+    </row>
+    <row r="190" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B190" s="2"/>
+      <c r="C190" s="2"/>
+      <c r="D190" s="2"/>
+      <c r="E190" s="2"/>
+      <c r="F190" s="2"/>
+      <c r="G190" s="2"/>
+    </row>
+    <row r="191" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B191" s="2"/>
+      <c r="C191" s="2"/>
+      <c r="D191" s="2"/>
+      <c r="E191" s="2"/>
+      <c r="F191" s="2"/>
+      <c r="G191" s="2"/>
+    </row>
+    <row r="192" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B192" s="2"/>
+      <c r="C192" s="2"/>
+      <c r="D192" s="2"/>
+      <c r="E192" s="2"/>
+      <c r="F192" s="2"/>
+      <c r="G192" s="2"/>
+    </row>
+    <row r="193" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B193" s="2"/>
+      <c r="C193" s="2"/>
+      <c r="D193" s="2"/>
+      <c r="E193" s="2"/>
+      <c r="F193" s="2"/>
+      <c r="G193" s="2"/>
+    </row>
+    <row r="194" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B194" s="2"/>
+      <c r="C194" s="2"/>
+      <c r="D194" s="2"/>
+      <c r="E194" s="2"/>
+      <c r="F194" s="2"/>
+      <c r="G194" s="2"/>
+    </row>
+    <row r="195" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B195" s="2"/>
+      <c r="C195" s="2"/>
+      <c r="D195" s="2"/>
+      <c r="E195" s="2"/>
+      <c r="F195" s="2"/>
+      <c r="G195" s="2"/>
+    </row>
+    <row r="196" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B196" s="2"/>
+      <c r="C196" s="2"/>
+      <c r="D196" s="2"/>
+      <c r="E196" s="2"/>
+      <c r="F196" s="2"/>
+      <c r="G196" s="2"/>
+    </row>
+    <row r="197" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B197" s="2"/>
+      <c r="C197" s="2"/>
+      <c r="D197" s="2"/>
+      <c r="E197" s="2"/>
+      <c r="F197" s="2"/>
+      <c r="G197" s="2"/>
+    </row>
+    <row r="198" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B198" s="2"/>
+      <c r="C198" s="2"/>
+      <c r="D198" s="2"/>
+      <c r="E198" s="2"/>
+      <c r="F198" s="2"/>
+      <c r="G198" s="2"/>
+    </row>
+    <row r="199" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B199" s="2"/>
+      <c r="C199" s="2"/>
+      <c r="D199" s="2"/>
+      <c r="E199" s="2"/>
+      <c r="F199" s="2"/>
+      <c r="G199" s="2"/>
+    </row>
+    <row r="200" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B200" s="2"/>
+      <c r="C200" s="2"/>
+      <c r="D200" s="2"/>
+      <c r="E200" s="2"/>
+      <c r="F200" s="2"/>
+      <c r="G200" s="2"/>
+    </row>
+    <row r="201" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B201" s="2"/>
+      <c r="C201" s="2"/>
+      <c r="D201" s="2"/>
+      <c r="E201" s="2"/>
+      <c r="F201" s="2"/>
+      <c r="G201" s="2"/>
+    </row>
+    <row r="202" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B202" s="2"/>
+      <c r="C202" s="2"/>
+      <c r="D202" s="2"/>
+      <c r="E202" s="2"/>
+      <c r="F202" s="2"/>
+      <c r="G202" s="2"/>
+    </row>
+    <row r="203" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B203" s="2"/>
+      <c r="C203" s="2"/>
+      <c r="D203" s="2"/>
+      <c r="E203" s="2"/>
+      <c r="F203" s="2"/>
+      <c r="G203" s="2"/>
+    </row>
+    <row r="204" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B204" s="2"/>
+      <c r="C204" s="2"/>
+      <c r="D204" s="2"/>
+      <c r="E204" s="2"/>
+      <c r="F204" s="2"/>
+      <c r="G204" s="2"/>
+    </row>
+    <row r="205" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B205" s="2"/>
+      <c r="C205" s="2"/>
+      <c r="D205" s="2"/>
+      <c r="E205" s="2"/>
+      <c r="F205" s="2"/>
+      <c r="G205" s="2"/>
+    </row>
+    <row r="206" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B206" s="2"/>
+      <c r="C206" s="2"/>
+      <c r="D206" s="2"/>
+      <c r="E206" s="2"/>
+      <c r="F206" s="2"/>
+      <c r="G206" s="2"/>
+    </row>
+    <row r="207" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B207" s="2"/>
+      <c r="C207" s="2"/>
+      <c r="D207" s="2"/>
+      <c r="E207" s="2"/>
+      <c r="F207" s="2"/>
+      <c r="G207" s="2"/>
+    </row>
+    <row r="208" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B208" s="2"/>
+      <c r="C208" s="2"/>
+      <c r="D208" s="2"/>
+      <c r="E208" s="2"/>
+      <c r="F208" s="2"/>
+      <c r="G208" s="2"/>
+    </row>
   </sheetData>
   <autoFilter ref="B2:G2" xr:uid="{87CB5822-66D4-452B-A3EB-3E11EDA85BE8}"/>
   <dataConsolidate/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1 F3:F1048576" xr:uid="{DBECB60C-6B8F-4EC4-BC7D-BFDD3056BA1F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C1048576" xr:uid="{EDCAA82B-601E-47FC-A7B2-54A6F21BB3AA}">
+      <formula1>"חשיבה פסיכומטרית, ספר אלגברה וגיאומטריה, ספר שאלות ובעיות, גל 1, גל 2, גל 3, בחנים חמים מהתנור, סימולציה 1, סימולציה 2, סימולציה 3, סימולציה 4, סימולציה 5, סימולציה 6, סימולציה 7, סימולציה 8, סימולציה 9"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F1048576" xr:uid="{A9925260-C1A9-4F00-BA4B-644F59B54188}">
       <formula1>"ידע, הבנה, כאפה"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576" xr:uid="{7BF493EB-AF19-4587-8B44-8C950A4B16A0}">
-      <formula1>"חשיבה פסיכומטרית, ספר אלגברה וגיאומטריה, ספר שאלות ובעיות, גל 1, גל 2, גל 3, בחנים חמים מהתנור, סימולציה 1, סימולציה 2, סימולציה 3, סימולציה 4, סימולציה 5, סימולציה 6, סימולציה 7, סימולציה 8, סימולציה 9"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -427,19 +2848,27 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E132A91-BD63-4135-BD52-EC7AF5CEDAC9}">
-  <dimension ref="B2:G2"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88CC7BBC-4307-46CC-87C2-2BBBAF65AAED}">
+  <dimension ref="B1:G5"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="40.69921875" customWidth="1"/>
-    <col min="3" max="3" width="18.69921875" customWidth="1"/>
-    <col min="4" max="4" width="17.69921875" customWidth="1"/>
-    <col min="5" max="5" width="40.69921875" customWidth="1"/>
-    <col min="6" max="6" width="17.69921875" customWidth="1"/>
-    <col min="7" max="7" width="40.69921875" customWidth="1"/>
+    <col min="2" max="2" width="40.69921875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18.69921875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.69921875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="40.69921875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.69921875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="40.69921875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B1"/>
+      <c r="C1"/>
+      <c r="D1"/>
+      <c r="E1"/>
+      <c r="F1"/>
+      <c r="G1"/>
+    </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>4</v>
@@ -458,16 +2887,169 @@
       </c>
       <c r="G2" s="1" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+    </row>
+    <row r="4" spans="2:7" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B2:G2" xr:uid="{87CB5822-66D4-452B-A3EB-3E11EDA85BE8}"/>
   <dataConsolidate/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576" xr:uid="{46599F15-22B1-4A6F-8280-973AC6F2DAC4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C1048576" xr:uid="{852F9983-5F7B-4FBC-87FF-DE3E258285C5}">
       <formula1>"חשיבה פסיכומטרית, ספר אלגברה וגיאומטריה, ספר שאלות ובעיות, גל 1, גל 2, גל 3, בחנים חמים מהתנור, סימולציה 1, סימולציה 2, סימולציה 3, סימולציה 4, סימולציה 5, סימולציה 6, סימולציה 7, סימולציה 8, סימולציה 9"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1 F3:F1048576" xr:uid="{08FF2842-B413-4AD5-897E-72A800DCD2B8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F1048576" xr:uid="{B75D0C48-C49C-4DAE-83AF-1907AE4FA027}">
+      <formula1>"ידע, הבנה, כאפה"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A38DD4A-CC61-47E7-A8D9-80343FFC1CCE}">
+  <dimension ref="B1:G5"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="40.69921875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18.69921875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.69921875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="40.69921875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.69921875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="40.69921875" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B1"/>
+      <c r="C1"/>
+      <c r="D1"/>
+      <c r="E1"/>
+      <c r="F1"/>
+      <c r="G1"/>
+    </row>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+    </row>
+    <row r="4" spans="2:7" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B2:G2" xr:uid="{87CB5822-66D4-452B-A3EB-3E11EDA85BE8}"/>
+  <dataConsolidate/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C1048576" xr:uid="{D211089B-DC4D-4671-8ACF-539C628E8176}">
+      <formula1>"ספר חשיבה פסיכומטרית, ספר אלגברה וגיאומטריה, ספר שאלות ובעיות, גל 1, גל 2, גל 3, בחנים חמים מהתנור, סימולציה 1, סימולציה 2, סימולציה 3, סימולציה 4, סימולציה 5, סימולציה 6, סימולציה 7, סימולציה 8, סימולציה 9"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F1048576" xr:uid="{D775A3D8-A764-467D-AEE9-B4A37864DB23}">
       <formula1>"ידע, הבנה, כאפה"</formula1>
     </dataValidation>
   </dataValidations>
